--- a/main/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="110">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Type de participation</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-hl7-v3-ParticipationType-cisis (2.16.840.1.113883.1.11.10901)</t>
@@ -1161,13 +1164,13 @@
         <v>73</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>73</v>
@@ -1202,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1231,10 +1234,10 @@
         <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1261,13 +1264,13 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
@@ -1285,7 +1288,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1302,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1328,13 +1331,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1385,7 +1388,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1402,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1428,13 +1431,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1485,7 +1488,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>85</v>
@@ -1502,10 +1505,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1528,13 +1531,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1585,7 +1588,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1602,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1628,13 +1631,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1685,7 +1688,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1702,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1728,13 +1731,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1785,7 +1788,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
